--- a/Result/profitability/6155.xlsx
+++ b/Result/profitability/6155.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21125</v>
+        <v>0.26</v>
       </c>
       <c r="N2" t="n">
-        <v>26.5</v>
+        <v>27.0975</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26125</v>
+        <v>0.33</v>
       </c>
       <c r="N3" t="n">
-        <v>28.925</v>
+        <v>29.33125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.34375</v>
+        <v>0.37125</v>
       </c>
       <c r="N4" t="n">
-        <v>31.39625</v>
+        <v>31.5875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>0.325</v>
+        <v>0.48875</v>
       </c>
       <c r="N5" t="n">
-        <v>32.835</v>
+        <v>33.0125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.44875</v>
+        <v>0.44625</v>
       </c>
       <c r="N6" t="n">
-        <v>33.495</v>
+        <v>34.00125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.68</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45125</v>
+        <v>0.49</v>
       </c>
       <c r="N7" t="n">
-        <v>35.785</v>
+        <v>36.22625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.84</v>
       </c>
       <c r="M8" t="n">
-        <v>0.515</v>
+        <v>0.5725</v>
       </c>
       <c r="N8" t="n">
-        <v>37.9025</v>
+        <v>37.94125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.55375</v>
       </c>
       <c r="N12" t="n">
-        <v>37.65000000000001</v>
+        <v>37.65</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6155</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>210</v>
+      </c>
+      <c r="D75" t="n">
+        <v>153</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>61</v>
+      </c>
+      <c r="K75" t="n">
+        <v>56</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.73125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.555555555555556</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3099999999999987</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01157580283793869</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.955223880597015</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.419999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05531749123490459</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
